--- a/docs/Danh_Sach_Nguoi_Dung_Import.xlsx
+++ b/docs/Danh_Sach_Nguoi_Dung_Import.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdqa7\Documents\CoopBank_Project\Contract_Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdqa7\Documents\CoopBank_Project\Contract_Management\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5654F5B-2E49-4725-BBB6-F90132DB6214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE4144-C26F-4AB0-842E-A466415733B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14370" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh Sách Người Dùng" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="396">
   <si>
     <t>Username</t>
   </si>
@@ -154,9 +154,6 @@
     <t>09123456789</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>NhanVien</t>
   </si>
   <si>
@@ -166,10 +163,13 @@
     <t>Bùi Thị Hồng Nhung</t>
   </si>
   <si>
+    <t>Chuyên viên - Phòng Core Banking và Ngân hàng số</t>
+  </si>
+  <si>
     <t>Chuyên viên</t>
   </si>
   <si>
-    <t>Phòng Công nghệ thông tin</t>
+    <t>Phòng Core Banking và Ngân hàng số</t>
   </si>
   <si>
     <t>nhungbth@co-opbank.vn</t>
@@ -382,9 +382,15 @@
     <t>Phạm Hồng Cường</t>
   </si>
   <si>
+    <t>Trưởng phòng - Phòng Quản trị vận hành ứng dụng</t>
+  </si>
+  <si>
     <t>Trưởng phòng</t>
   </si>
   <si>
+    <t>Phòng Quản trị vận hành ứng dụng</t>
+  </si>
+  <si>
     <t>cuongph@co-opbank.vn</t>
   </si>
   <si>
@@ -400,6 +406,9 @@
     <t>Đỗ Phương Quang</t>
   </si>
   <si>
+    <t>Phó phòng - Phòng Quản trị vận hành ứng dụng</t>
+  </si>
+  <si>
     <t>Phó phòng</t>
   </si>
   <si>
@@ -433,6 +442,9 @@
     <t>Đỗ Thị Thanh Huyền</t>
   </si>
   <si>
+    <t>Chuyên viên - Phòng Quản trị vận hành ứng dụng</t>
+  </si>
+  <si>
     <t>huyendtt@co-opbank.vn</t>
   </si>
   <si>
@@ -553,6 +565,12 @@
     <t>Đỗ Gia Hoàng</t>
   </si>
   <si>
+    <t>Chuyên viên - Phòng Quản trị vận hành hạ tầng công nghệ</t>
+  </si>
+  <si>
+    <t>Phòng Quản trị vận hành hạ tầng công nghệ</t>
+  </si>
+  <si>
     <t>hoangdg@co-opbank.vn</t>
   </si>
   <si>
@@ -673,6 +691,12 @@
     <t>Luyện Công Nam</t>
   </si>
   <si>
+    <t>Trưởng phòng  - Phòng An ninh Bảo mật mạng</t>
+  </si>
+  <si>
+    <t>Phòng An ninh Bảo mật mạng</t>
+  </si>
+  <si>
     <t>namlc@co-opbank.vn</t>
   </si>
   <si>
@@ -688,6 +712,9 @@
     <t>Nguyễn Anh Tuấn</t>
   </si>
   <si>
+    <t>Phó phòng  - Phòng An ninh Bảo mật mạng</t>
+  </si>
+  <si>
     <t>tuanna2@co-opbank.vn</t>
   </si>
   <si>
@@ -703,6 +730,9 @@
     <t>Đào Trọng Bách</t>
   </si>
   <si>
+    <t>Chuyên viên - Phòng Phòng An ninh Bảo mật mạng</t>
+  </si>
+  <si>
     <t>bachdt@co-opbank.vn</t>
   </si>
   <si>
@@ -877,6 +907,12 @@
     <t>Nguyễn Đình Sơn</t>
   </si>
   <si>
+    <t>Trưởng phòng   - Phòng Thông tin báo cáo - Tổng hợp</t>
+  </si>
+  <si>
+    <t>Phòng Thông tin báo cáo - Tổng hợp</t>
+  </si>
+  <si>
     <t>sonnd@co-opbank.vn</t>
   </si>
   <si>
@@ -892,6 +928,9 @@
     <t>Nguyễn Phương Mai</t>
   </si>
   <si>
+    <t>Phó phòng  - Phòng Thông tin báo cáo - Tổng hợp</t>
+  </si>
+  <si>
     <t>mainp@co-opbank.vn</t>
   </si>
   <si>
@@ -907,6 +946,9 @@
     <t>Phan Thùy Chi</t>
   </si>
   <si>
+    <t>Phó phòng   - Phòng Thông tin báo cáo - Tổng hợp</t>
+  </si>
+  <si>
     <t>chipt@co-opbank.vn</t>
   </si>
   <si>
@@ -919,9 +961,6 @@
     <t>phongkt4</t>
   </si>
   <si>
-    <t>Phòng Thông tin báo cáo - Tổng hợp</t>
-  </si>
-  <si>
     <t>- Phòng Thông tin báo cáo - Tổng hợp</t>
   </si>
   <si>
@@ -949,6 +988,9 @@
     <t>Nguyễn Hữu Thành</t>
   </si>
   <si>
+    <t>Chuyên viên - Phòng Thông tin báo cáo - Tổng hợp</t>
+  </si>
+  <si>
     <t>thanhnh@co-opbank.vn</t>
   </si>
   <si>
@@ -1165,47 +1207,14 @@
     <t>12/02/1981</t>
   </si>
   <si>
-    <t>Chuyên viên - Phòng Core Banking và Ngân hàng số</t>
-  </si>
-  <si>
-    <t>Chuyên viên - Phòng Quản trị vận hành ứng dụng</t>
-  </si>
-  <si>
-    <t>Chuyên viên - Phòng Quản trị vận hành hạ tầng công nghệ</t>
-  </si>
-  <si>
-    <t>Chuyên viên - Phòng Phòng An ninh Bảo mật mạng</t>
-  </si>
-  <si>
-    <t>Chuyên viên - Phòng Thông tin báo cáo - Tổng hợp</t>
-  </si>
-  <si>
-    <t>Trưởng phòng - Phòng Quản trị vận hành ứng dụng</t>
-  </si>
-  <si>
-    <t>Phó phòng - Phòng Quản trị vận hành ứng dụng</t>
-  </si>
-  <si>
-    <t>Trưởng phòng  - Phòng An ninh Bảo mật mạng</t>
-  </si>
-  <si>
-    <t>Phó phòng  - Phòng An ninh Bảo mật mạng</t>
-  </si>
-  <si>
-    <t>Trưởng phòng   - Phòng Thông tin báo cáo - Tổng hợp</t>
-  </si>
-  <si>
-    <t>Phó phòng  - Phòng Thông tin báo cáo - Tổng hợp</t>
-  </si>
-  <si>
-    <t>Phó phòng   - Phòng Thông tin báo cáo - Tổng hợp</t>
+    <t>Đơn vị</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1213,316 +1222,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1530,204 +1239,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2039,16 +1559,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="31.7109375" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2083,10 +1605,13 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2121,10 +1646,13 @@
         <v>22</v>
       </c>
       <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2159,10 +1687,13 @@
         <v>22</v>
       </c>
       <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2197,10 +1728,13 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -2222,31 +1756,31 @@
       <c r="G5" t="s">
         <v>43</v>
       </c>
-      <c r="H5" t="s">
-        <v>44</v>
-      </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>381</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
@@ -2267,16 +1801,19 @@
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -2284,7 +1821,7 @@
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
@@ -2305,16 +1842,19 @@
         <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -2322,7 +1862,7 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
@@ -2343,16 +1883,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
         <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -2360,7 +1903,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -2381,16 +1924,19 @@
         <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -2398,7 +1944,7 @@
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
@@ -2419,16 +1965,19 @@
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
         <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -2436,7 +1985,7 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
@@ -2457,16 +2006,19 @@
         <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -2474,7 +2026,7 @@
         <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
@@ -2495,16 +2047,19 @@
         <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -2512,7 +2067,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
@@ -2533,16 +2088,19 @@
         <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -2550,7 +2108,7 @@
         <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
@@ -2571,16 +2129,19 @@
         <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K14" t="s">
         <v>22</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -2588,7 +2149,7 @@
         <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
@@ -2609,16 +2170,19 @@
         <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K15" t="s">
         <v>22</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -2626,7 +2190,7 @@
         <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
@@ -2647,16 +2211,19 @@
         <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K16" t="s">
         <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>103</v>
       </c>
@@ -2664,7 +2231,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
@@ -2685,16 +2252,19 @@
         <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
         <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>108</v>
       </c>
@@ -2702,7 +2272,7 @@
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
@@ -2723,16 +2293,19 @@
         <v>31</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K18" t="s">
         <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -2740,7 +2313,7 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
@@ -2761,16 +2334,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
         <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -2778,22 +2354,22 @@
         <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>386</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I20" t="s">
         <v>20</v>
@@ -2805,33 +2381,36 @@
         <v>22</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>387</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
@@ -2843,33 +2422,36 @@
         <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>387</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -2881,641 +2463,692 @@
         <v>22</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H23" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I23" t="s">
         <v>31</v>
       </c>
       <c r="J23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K23" t="s">
         <v>22</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" t="s">
         <v>140</v>
       </c>
-      <c r="B24" t="s">
-        <v>141</v>
-      </c>
-      <c r="C24" t="s">
-        <v>382</v>
-      </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
         <v>20</v>
       </c>
       <c r="J24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
         <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C25" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H25" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I25" t="s">
         <v>31</v>
       </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
         <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H26" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I26" t="s">
         <v>31</v>
       </c>
       <c r="J26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K26" t="s">
         <v>22</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I27" t="s">
         <v>20</v>
       </c>
       <c r="J27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K27" t="s">
         <v>22</v>
       </c>
       <c r="L27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H28" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I28" t="s">
         <v>20</v>
       </c>
       <c r="J28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K28" t="s">
         <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H29" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
         <v>20</v>
       </c>
       <c r="J29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K29" t="s">
         <v>22</v>
       </c>
       <c r="L29" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>382</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I30" t="s">
         <v>31</v>
       </c>
       <c r="J30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K30" t="s">
         <v>22</v>
       </c>
       <c r="L30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F31" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H31" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
       </c>
       <c r="J31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K31" t="s">
         <v>22</v>
       </c>
       <c r="L31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" t="s">
         <v>181</v>
       </c>
-      <c r="C32" t="s">
-        <v>383</v>
-      </c>
       <c r="D32" t="s">
         <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H32" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
       </c>
       <c r="J32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K32" t="s">
         <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
         <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F33" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G33" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H33" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I33" t="s">
         <v>20</v>
       </c>
       <c r="J33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K33" t="s">
         <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
         <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F34" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G34" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H34" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
         <v>20</v>
       </c>
       <c r="J34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K34" t="s">
         <v>22</v>
       </c>
       <c r="L34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F35" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H35" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I35" t="s">
         <v>20</v>
       </c>
       <c r="J35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K35" t="s">
         <v>22</v>
       </c>
       <c r="L35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C36" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
         <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G36" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H36" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I36" t="s">
         <v>20</v>
       </c>
       <c r="J36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K36" t="s">
         <v>22</v>
       </c>
       <c r="L36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C37" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
         <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G37" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H37" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
       </c>
       <c r="J37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K37" t="s">
         <v>22</v>
       </c>
       <c r="L37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G38" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H38" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="I38" t="s">
         <v>20</v>
       </c>
       <c r="J38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K38" t="s">
         <v>22</v>
       </c>
       <c r="L38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C39" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>224</v>
       </c>
       <c r="F39" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G39" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H39" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I39" t="s">
         <v>20</v>
@@ -3527,33 +3160,36 @@
         <v>22</v>
       </c>
       <c r="L39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C40" t="s">
-        <v>389</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G40" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I40" t="s">
         <v>20</v>
@@ -3565,489 +3201,522 @@
         <v>22</v>
       </c>
       <c r="L40" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F41" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G41" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H41" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
       </c>
       <c r="J41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K41" t="s">
         <v>22</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B42" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C42" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
         <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F42" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G42" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H42" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I42" t="s">
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K42" t="s">
         <v>22</v>
       </c>
       <c r="L42" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B43" t="s">
+        <v>246</v>
+      </c>
+      <c r="C43" t="s">
         <v>236</v>
       </c>
-      <c r="C43" t="s">
-        <v>384</v>
-      </c>
       <c r="D43" t="s">
         <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F43" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G43" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="H43" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
       </c>
       <c r="J43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K43" t="s">
         <v>22</v>
       </c>
       <c r="L43" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B44" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C44" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>242</v>
-      </c>
-      <c r="G44" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="I44" t="s">
         <v>31</v>
       </c>
       <c r="J44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K44" t="s">
         <v>22</v>
       </c>
       <c r="L44" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D45" t="s">
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F45" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G45" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="H45" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
       <c r="J45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K45" t="s">
         <v>22</v>
       </c>
       <c r="L45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D46" t="s">
         <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G46" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H46" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
       <c r="J46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K46" t="s">
         <v>22</v>
       </c>
       <c r="L46" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D47" t="s">
         <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F47" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G47" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H47" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
       <c r="J47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K47" t="s">
         <v>22</v>
       </c>
       <c r="L47" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B48" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C48" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F48" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G48" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="H48" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
       <c r="J48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K48" t="s">
         <v>22</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B49" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C49" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
         <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F49" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G49" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H49" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
       <c r="J49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K49" t="s">
         <v>22</v>
       </c>
       <c r="L49" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C50" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D50" t="s">
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G50" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I50" t="s">
         <v>20</v>
       </c>
       <c r="J50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K50" t="s">
         <v>22</v>
       </c>
       <c r="L50" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B51" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C51" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D51" t="s">
         <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F51" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="G51" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="H51" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I51" t="s">
         <v>20</v>
       </c>
       <c r="J51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K51" t="s">
         <v>22</v>
       </c>
       <c r="L51" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
         <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F52" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G52" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H52" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
       </c>
       <c r="J52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K52" t="s">
         <v>22</v>
       </c>
       <c r="L52" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C53" t="s">
-        <v>390</v>
+        <v>295</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F53" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G53" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="H53" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
@@ -4059,33 +3728,36 @@
         <v>22</v>
       </c>
       <c r="L53" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C54" t="s">
-        <v>391</v>
+        <v>302</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F54" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="G54" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H54" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="I54" t="s">
         <v>31</v>
@@ -4097,33 +3769,36 @@
         <v>22</v>
       </c>
       <c r="L54" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C55" t="s">
-        <v>392</v>
+        <v>308</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E55" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F55" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="G55" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="H55" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="I55" t="s">
         <v>31</v>
@@ -4135,652 +3810,700 @@
         <v>22</v>
       </c>
       <c r="L55" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B56" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C56" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D56" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E56" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="G56" t="s">
+        <v>310</v>
+      </c>
+      <c r="I56" t="s">
+        <v>316</v>
+      </c>
+      <c r="J56" t="s">
+        <v>44</v>
+      </c>
+      <c r="K56" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" t="s">
+        <v>16</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" t="s">
+        <v>318</v>
+      </c>
+      <c r="C57" t="s">
+        <v>313</v>
+      </c>
+      <c r="D57" t="s">
+        <v>314</v>
+      </c>
+      <c r="E57" t="s">
         <v>296</v>
       </c>
-      <c r="H56" t="s">
-        <v>44</v>
-      </c>
-      <c r="I56" t="s">
-        <v>303</v>
-      </c>
-      <c r="J56" t="s">
-        <v>45</v>
-      </c>
-      <c r="K56" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>304</v>
-      </c>
-      <c r="B57" t="s">
-        <v>305</v>
-      </c>
-      <c r="C57" t="s">
-        <v>300</v>
-      </c>
-      <c r="D57" t="s">
-        <v>301</v>
-      </c>
-      <c r="E57" t="s">
-        <v>299</v>
-      </c>
       <c r="F57" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>198</v>
-      </c>
-      <c r="H57" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="I57" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="J57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K57" t="s">
         <v>22</v>
       </c>
       <c r="L57" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B58" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C58" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D58" t="s">
         <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F58" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="G58" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H58" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
       </c>
       <c r="J58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K58" t="s">
         <v>22</v>
       </c>
       <c r="L58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B59" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C59" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D59" t="s">
         <v>48</v>
       </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F59" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="G59" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="H59" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
       <c r="J59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K59" t="s">
         <v>22</v>
       </c>
       <c r="L59" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C60" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D60" t="s">
         <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="G60" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H60" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
       <c r="J60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K60" t="s">
         <v>22</v>
       </c>
       <c r="L60" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>336</v>
+      </c>
+      <c r="B61" t="s">
+        <v>337</v>
+      </c>
+      <c r="C61" t="s">
         <v>322</v>
       </c>
-      <c r="B61" t="s">
-        <v>323</v>
-      </c>
-      <c r="C61" t="s">
-        <v>385</v>
-      </c>
       <c r="D61" t="s">
         <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F61" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="G61" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="H61" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
       </c>
       <c r="J61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K61" t="s">
         <v>22</v>
       </c>
       <c r="L61" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C62" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D62" t="s">
         <v>48</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F62" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="G62" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="H62" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
       </c>
       <c r="J62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K62" t="s">
         <v>22</v>
       </c>
       <c r="L62" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B63" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
         <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F63" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="G63" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="H63" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
       </c>
       <c r="J63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K63" t="s">
         <v>22</v>
       </c>
       <c r="L63" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C64" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D64" t="s">
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F64" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="G64" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="H64" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="I64" t="s">
         <v>31</v>
       </c>
       <c r="J64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K64" t="s">
         <v>22</v>
       </c>
       <c r="L64" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C65" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D65" t="s">
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F65" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="G65" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="H65" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="I65" t="s">
         <v>20</v>
       </c>
       <c r="J65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K65" t="s">
         <v>22</v>
       </c>
       <c r="L65" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C66" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D66" t="s">
         <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F66" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="G66" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="H66" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="I66" t="s">
         <v>31</v>
       </c>
       <c r="J66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K66" t="s">
         <v>22</v>
       </c>
       <c r="L66" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C67" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D67" t="s">
         <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F67" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="G67" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="H67" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
       </c>
       <c r="J67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K67" t="s">
         <v>22</v>
       </c>
       <c r="L67" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C68" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D68" t="s">
         <v>48</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F68" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="G68" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="H68" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
       </c>
       <c r="J68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K68" t="s">
         <v>22</v>
       </c>
       <c r="L68" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B69" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C69" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D69" t="s">
         <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="G69" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="H69" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="I69" t="s">
         <v>20</v>
       </c>
       <c r="J69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K69" t="s">
         <v>22</v>
       </c>
       <c r="L69" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="C70" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D70" t="s">
         <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F70" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="G70" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="H70" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="I70" t="s">
         <v>31</v>
       </c>
       <c r="J70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K70" t="s">
         <v>22</v>
       </c>
       <c r="L70" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="C71" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D71" t="s">
         <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F71" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="G71" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="H71" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="I71" t="s">
         <v>31</v>
       </c>
       <c r="J71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K71" t="s">
         <v>22</v>
       </c>
       <c r="L71" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C72" t="s">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D72" t="s">
         <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F72" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="G72" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="H72" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="I72" t="s">
         <v>31</v>
       </c>
       <c r="J72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K72" t="s">
         <v>22</v>
       </c>
       <c r="L72" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" t="s">
         <v>37</v>
       </c>
     </row>
